--- a/files/NUR-Lecture-Library.xlsx
+++ b/files/NUR-Lecture-Library.xlsx
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="D6" s="80">
-        <f>HYPERLINK("https://cdn.fbsbx.com/v/t59.2708-21/709134506_996324786129503_9201132740511638709_n.pdf/235_Exam1-Practice-Test.pdf?_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=2b0e22&amp;_nc_ohc=AbmvM3Y_ss0Q7kNvwF4rBAp&amp;_nc_oc=Ado3Z4hwaBTAslL-RWNPR0cznsC6r1fLuD9yK_iQf2yPvllACKypwHVrG1IQgHfvH"&amp;"Ns&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=7&amp;_nc_ht=cdn.fbsbx.com&amp;_nc_gid=kVYujx6SmV2z2IRTZBkvhw&amp;_nc_ss=7a338&amp;oh=03_Q7cD5QEx_w8ZwEWF8ZKNQzA0i61GMt76YH9msmrIHMebB5rwxg&amp;oe=6A1A2F27&amp;dl=1","🔗  Open")</f>
+        <f>HYPERLINK("https://drive.google.com/file/d/1Yv94xKT8ZGHW1GnrXWKFS0_AD8U-WOqr/view","🔗  Open")</f>
         <v/>
       </c>
       <c r="E6" s="79" t="inlineStr">
@@ -25982,7 +25982,7 @@
         </is>
       </c>
       <c r="F6" s="70">
-        <f>HYPERLINK("https://cdn.fbsbx.com/v/t59.2708-21/708926269_3043975365993301_8004983880842006455_n.pdf/NUR234_Exam1_Maternal_Study_Guide-1-2.pdf?_nc_cat=102&amp;ccb=1-7&amp;_nc_sid=2b0e22&amp;_nc_ohc=ANCb2W3akjcQ7kNvwEFm7IR&amp;_nc_oc=AdroCix-bq3q94V78qldDADiGj8yYe4iokRmY6DUrw9FBUeYva"&amp;"NitZGWjsC76Jxp87g&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=7&amp;_nc_ht=cdn.fbsbx.com&amp;_nc_gid=A0gOfdvKIG-Ht3lFaXA7bg&amp;_nc_ss=7a338&amp;oh=03_Q7cD5QErvnov4_QnTHOdYMn_Oj-Gh8XaB1YpONRGKa-9sYwQ9Q&amp;oe=6A19481D&amp;dl=1","🔗  Open")</f>
+        <f>HYPERLINK("https://drive.google.com/file/d/1G-isAusr4xSiEajdswjxRKPg2ZXah-E9/view","🔗  Open")</f>
         <v/>
       </c>
       <c r="G6" s="55" t="inlineStr">
@@ -26014,7 +26014,7 @@
         </is>
       </c>
       <c r="F7" s="72">
-        <f>HYPERLINK("https://cdn.fbsbx.com/v/t59.2708-21/709662661_1351782883462413_4943038801683447033_n.pdf/234_Exam-1-Practice-Test.pdf?_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=2b0e22&amp;_nc_ohc=MfE4Yc95S5gQ7kNvwGWFGua&amp;_nc_oc=AdrA2UMRN_HAL4Ly3DANkdvs-g5YCXQ7k2VS_ouOuFEJXbEy6QsOF5hgnNKFFwx"&amp;"8z1g&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=7&amp;_nc_ht=cdn.fbsbx.com&amp;_nc_gid=Ee0sDUO32YXbTQSLgh61tg&amp;_nc_ss=7a338&amp;oh=03_Q7cD5QEFGFm2z4Fl5svDzOKLGuJtkYPFnVd9vCsqDBVhfOsi1A&amp;oe=6A1BA46B&amp;dl=1","🔗  Open")</f>
+        <f>HYPERLINK("https://drive.google.com/file/d/18sXhH2IZ8qhFlQThhjENr3rB-P8La9BX/view","🔗  Open")</f>
         <v/>
       </c>
       <c r="G7" s="35" t="inlineStr">

--- a/files/NUR-Lecture-Library.xlsx
+++ b/files/NUR-Lecture-Library.xlsx
@@ -30115,12 +30115,12 @@
         </is>
       </c>
       <c r="E7" s="80">
-        <f>HYPERLINK("https://drive.google.com/file/d/1yRquegiEz7A7eN-ms2smuTgrVaeivjoE/view","▶  Watch")</f>
+        <f>HYPERLINK("https://drive.google.com/file/d/1LlXr19xnRaDRvh2CaY0NTa5m33OeLVNw/view","▶  Watch")</f>
         <v/>
       </c>
       <c r="F7" s="79" t="inlineStr">
         <is>
-          <t>Nur235_Fuller_Wk2.mp4</t>
+          <t>NUR235_Fall2026_Fuller_Wk02_DayNA_Week 2 Check-In.mp4</t>
         </is>
       </c>
       <c r="G7" s="83" t="inlineStr">
